--- a/paper/Table_Studies.xlsx
+++ b/paper/Table_Studies.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -15,7 +15,23 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -31,9 +47,27 @@
     <t>journal</t>
   </si>
   <si>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Study design</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
     <t>n</t>
   </si>
   <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Main focus</t>
+  </si>
+  <si>
     <t>age_class</t>
   </si>
   <si>
@@ -49,6 +83,465 @@
     <t>notes</t>
   </si>
   <si>
+    <t>https://doi.org/10.1016/j.paid.2024.112870</t>
+  </si>
+  <si>
+    <t>Past research has demonstrated that university students with a stronger sense of purpose tend to fare better than their peers. However, work is needed to investigate the mechanisms and skills that may underlie these associations. The current studies employed two university student samples (total n = 412) and comprehensively investigated associations between sense of purpose and social-emotional-behavioral skills, using multiple purpose measures. Associations were relatively similar across measures and samples, and results suggested that sense of purpose was most robustly positively associated with self-management skills. Sense of purpose also was associated with better student wellbeing (life satisfaction, college satisfaction, and student connectedness), though it was inconsistently associated with reported likelihood of degree completion. Sense of purpose largely remained a significant correlate of student wellbeing, even when accounting for SEB skill domains, although some associations between purpose and wellbeing were reduced in magnitude.</t>
+  </si>
+  <si>
+    <t>PERSONALITY AND INDIVIDUAL DIFFERENCES</t>
+  </si>
+  <si>
+    <t>Beatty et al.</t>
+  </si>
+  <si>
+    <t>Cross-sectional</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>Young adults</t>
+  </si>
+  <si>
+    <t>Associations between sense of purpose and SEB skills in university students</t>
+  </si>
+  <si>
+    <t>young_adult</t>
+  </si>
+  <si>
+    <t>not_clinical</t>
+  </si>
+  <si>
+    <t>bessi96</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>Only cor between skills and outcomes available</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3390/jintelligence10030048</t>
+  </si>
+  <si>
+    <t>Social skills are of key importance in everyday and work life. However, the way in which they are typically assessed via self-report questionnaires has one potential downside</t>
+  </si>
+  <si>
+    <t>JOURNAL OF INTELLIGENCE</t>
+  </si>
+  <si>
+    <t>Breil et al.</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Associations between self- and observer- reports for three social skills</t>
+  </si>
+  <si>
+    <t>bessi192</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1525/collabra.120531</t>
+  </si>
+  <si>
+    <t>The current study sought to extend Soto et al. (2022)'s results on social, emotional, and behavioral (SEB) skills to a work setting and answer three key questions. First, do SEB skills predict consequential work-related outcomes? Second, do SEB skills provide incremental validity over the Big Five personality traits in predicting the outcomes? Third, is the joint effect of SEB skills and traits additive or multiplicative? Results from a sample of real estate agents (N N = 2,992) in China extend the criterion space of SEB skills by showing self-concepts of these skills are related to self-reported work outcomes such as citizenship behaviors and job satisfaction in a conceptually meaningful way. Further analyses show that these skill-outcome relationships remain robust after accounting for effects of traits, indicating SEB skills' incremental validity beyond traits in predicting outcomes. Finally, comparisons between additive and multiplicative models show support for the former because the interaction effects of SEB skills and traits provide little meaningful information beyond the additive models. Based on these findings, we discuss the implications for the SEB skills literature and practice.</t>
+  </si>
+  <si>
+    <t>COLLABRA-PSYCHOLOGY</t>
+  </si>
+  <si>
+    <t>Chen et al.</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>Adults</t>
+  </si>
+  <si>
+    <t>SEB skills and their incremental validity for job outcomes beyond personality traits</t>
+  </si>
+  <si>
+    <t>adult</t>
+  </si>
+  <si>
+    <t>bessi45</t>
+  </si>
+  <si>
+    <t>short</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s11218-025-10079-9</t>
+  </si>
+  <si>
+    <t>In this study, we investigated perceived social-emotional competence (PSEC) among 373 Australian secondary school students in relation to parent ratings of social-emotional skills, and perceived teacher and parental autonomy support. Using bifactor exploratory structural equation modelling, we examined five dimensions of PSEC (perceived competence for assertiveness, tolerance, social regulation, emotion regulation, and emotional awareness), identifying a global factor and five specific factors. Following that, we employed structural equation modelling to investigate links between these global and specific factors and five parent-reported social-emotional skills: leadership, cultural competence, teamwork, cognitive reappraisal, and capacity for emotional reflection. Global PSEC was associated positively with all skills, whereas the specific factors were, with one exception, each associated with greater parent-rated skill in a corresponding area (e.g., assertiveness with greater leadership skill; emotion awareness with reflective skills). Addressing a second aim of the research, we tested the extent to which students’ perceptions of autonomy support from teachers and parents assessed near the start of a school term were associated with both students’ PSEC and parent-rated skills assessed at the end of the term. Autonomy-supportive parenting was positively associated with global PSEC. Autonomy-supportive teaching was associated with greater levels of two specific factors: perceived competence for assertiveness and social regulation. Together, findings hold relevance to knowledge and efforts aimed at enhancing social-emotional skills among students.</t>
+  </si>
+  <si>
+    <t>Social Psychology of Education</t>
+  </si>
+  <si>
+    <t>Collie &amp; Ryan</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Secondary school</t>
+  </si>
+  <si>
+    <t>Parent-rated SEB skills and their associations with children perceived socio-emotional competence and autonomy support</t>
+  </si>
+  <si>
+    <t>school_age</t>
+  </si>
+  <si>
+    <t>bessi_otherReport</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1177/20965311251319355</t>
+  </si>
+  <si>
+    <t>Purpose This review paper addresses three major challenges hindering progress in the field of social-emotional learning in education.Design/Approach/Methods We first discuss how social-emotional skills could be conceptualized, contrasting identity versus self-efficacy approaches. Second, we argue to develop more objective assessments of social-emotional skills and their development, as a supplement of currently and frequently used self- and informant descriptions relying on Likert-based scales. Third and finally, we discuss recurrent issues that are raised when debating the implementation of social-emotional skill learning in the classroom.Findings The review suggests that, at this point in time, both self-efficacy and identity conceptualizations of social-emotional skills are valuable approaches. Future research will need to explore which conceptualization for which skills demonstrates the best predictive validity, taking into account the nature of outcomes and contexts. The desired characteristics of more objective social-emotional skill measures are defined, and we encourage to examine how these overlap with self-reports using construct maps. Finally, we underscore the importance of having a comprehensive and evidence-informed taxonomy of social-emotional skills to guide the debate on the inclusion of social-emotional skill learning in curricula and its implementation in the classroom.Originality/Value This short review is primarily written for practitioners and policymakers to give a quick and accessible update on the key challenges in social-emotional learning today. The review should trigger more in-depth reading on the topic, but also support readers to understand current problems and help them dealing with questions and potential objections that might be raised by different stakeholders.</t>
+  </si>
+  <si>
+    <t>ECNU REVIEW OF EDUCATION</t>
+  </si>
+  <si>
+    <t>De Fruyt et al.</t>
+  </si>
+  <si>
+    <t>Theoretical</t>
+  </si>
+  <si>
+    <t>Conceptual and methodological challenges in SEB skills assessment and interventions</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3390/jintelligence11060118</t>
+  </si>
+  <si>
+    <t>Individuals use social, emotional, and behavioral (SEB) skills to build and maintain social relationships, regulate emotions, and manage goal-directed behaviors. A promising integrative framework of SEB skills was recently proposed, showing that they matter for positive outcomes during adolescence. Nothing is known about how and whether they differ between 12 and 19 years old and whether such differences depend on gender (males or females). Uncovering their age trajectories is fundamental because SEB skills are highly needed during this period of life. Educators, psychologists, and policymakers need to understand when, why, and how interventions concerning SEB skills should be proposed, potentially considering male and female profiles. To cover this gap, we cross-sectionally analyzed data from 4106 participants (2215 females, 12-19 years old). We highlighted age and gender differences in the five domains of SEB skills (self-management, innovation, cooperation, social engagement, and emotional resilience). Our results show that each SEB skill follows a specific age trend: emotional resilience and cooperation skills increase naturally between 12 and 19 years old, while innovation, social engagement, and self-management skills decline, especially between 12 and 16 years old, and grow later. The trajectories of self-management, social engagement, and emotional resilience skills also differ between males and females. Importantly, we detected declines in SEB skills (especially for social engagement and innovation skills) that can inform policies and interventions to sustain SEB skills in youths to favor their well-being and success in this crucial period.</t>
+  </si>
+  <si>
+    <t>Feraco &amp; Meneghetti</t>
+  </si>
+  <si>
+    <t>Germany, Italy, Unites States</t>
+  </si>
+  <si>
+    <t>Age and gender differences in SEB skills among adolescents</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.lindif.2024.102581</t>
+  </si>
+  <si>
+    <t>Social, emotional, and behavioral (SEB) skills are key factors for academic and non-academic outcomes, but no previous studies deepened SEB skills of students with specific learning disabilities (SLD). We used the Behavioral, Emotional, and Social Skills Inventory (BESSI) to systematically investigate i) differences in social engagement, self-management, innovation, emotional resilience, and cooperation skills and ii) the interaction effect between skills and group on academic achievement and life satisfaction. In a sample of 2965 students (1589 females, M = 15.5 years, SD = 2.0), 359 of whom reported a SLD, we found differences in self-management (d = -0.28), innovation (d = -0.25), and social engagement (d = -0.19) skills. Furthermore, higher SEB skills do not guarantee higher academic achievement in the SLD group, while their role is similar in the two groups for life satisfaction. Overall, students with SLD may benefit from interventions to improve knowledge and use of SEB skills.</t>
+  </si>
+  <si>
+    <t>LEARNING AND INDIVIDUAL DIFFERENCES</t>
+  </si>
+  <si>
+    <t>Feraco et al.</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>SEB skills in students with learning disabilities</t>
+  </si>
+  <si>
+    <t>clinical (specific learning disabilities)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1080/00223891.2024.2335912</t>
+  </si>
+  <si>
+    <t>The importance of social, emotional, and behavioral (SEB) skills is recognized worldwide, but their measurement has always been a challenge. The BESSI measures 32 SEB skills, divided into five domains (social engagement, cooperation, self-management, emotional resilience, and innovation), but its validity must be expanded to new languages and contexts. Across two studies (N1 = 990, N2= 824) we developed the Italian version of the BESSI, provided further support for its convergent and discriminant validity with the Big Five, and expanded its nomological network to procrastination, self-efficacy, and emotion regulation. The BESSI-I showed excellent internal reliability and satisfactory fit indices at the facet, domain, and overarching framework level. We also confirmed the correlations between the SEB skills and the Big Five personality traits and found meaningful correlations with the selected external outcomes. Overall, we confirm that the BESSI-I is a valid and useful instrument to assess SEB skills for research and clinical purposes.</t>
+  </si>
+  <si>
+    <t>JOURNAL OF PERSONALITY ASSESSMENT</t>
+  </si>
+  <si>
+    <t>Secondary school &amp; Adults</t>
+  </si>
+  <si>
+    <t>Validation of the Italian version of the BESSI</t>
+  </si>
+  <si>
+    <t>includes school age and adults</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.paid.2025.113200</t>
+  </si>
+  <si>
+    <t>Although research suggests that most people want to change their personality traits, previous studies have neither explored whether individuals also desire to change the social, emotional, and behavioral (SEB) skills linked to those traits, nor whether people have different beliefs about the malleability of skills vs. traits. In the present within-person experiment, 264 young adults from the US and Italy rated their desire to change each of the Big Five personality traits and the corresponding domains of SEB skills. They also rated their beliefs about the feasibility, motivation, and impact of making these changes. Results showed that participants reported similar or higher scores for skills, compared to traits, across all measured outcomes. Specifically, scores for social engagement and self-management skills were consistently higher than those for extraversion and conscientiousness. These findings indicate that people believe it to be more desirable-and more feasible-to change some SEB skills than the corresponding personality traits.</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>Italy, United States</t>
+  </si>
+  <si>
+    <t>Change goals and perceived feasibility about changing SEB skills vs traits</t>
+  </si>
+  <si>
+    <t>Change goals</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1080/13504622.2025.2459323</t>
+  </si>
+  <si>
+    <t>Following indications from international organizations, this study tests the associations between the five domains of social, emotional, and behavioral (SEB) skills (self-management, innovation, social engagement, cooperation, and emotional resilience) and two key antecedents of proenvironmental behavior, namely nature connectedness and self-perceived action competence for sustainability, in a sample of 702 students aged between 12 and 20 years (M = 16.18, SD = 2.15</t>
+  </si>
+  <si>
+    <t>ENVIRONMENTAL EDUCATION RESEARCH</t>
+  </si>
+  <si>
+    <t>SEB skills links to pro-environmental attitudes and behaviors</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s11218-025-10095-9</t>
+  </si>
+  <si>
+    <t>Social, emotional, and behavioral (SEB) skills- also known under labels like soft skills, 21st century skills, or social-emotional skills- are considered key factors for students' success, well-being, and social relationships, among others. However, literature on the topic relied on different frameworks and questionable measurement methods. Additionally, they usually did not integrate skills into classical self-regulated learning (SRL) frameworks. To overcome these limitations, we adopted the new integrative SEB framework and measured SEB skills, along with five SRL factors (academic self-efficacy, SRL strategies, mastery learning goals, growth mindset, and achievement emotions) and three outcomes (i.e., self-reported academic achievement, peer acceptance, and life satisfaction). Participants were 5,075 Italian high school students (M = 18.23 years old</t>
+  </si>
+  <si>
+    <t>SOCIAL PSYCHOLOGY OF EDUCATION</t>
+  </si>
+  <si>
+    <t>Associations between SEB skills and self-regulated learning factors</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10791-025-09703-1</t>
+  </si>
+  <si>
+    <t>New technologies, such as Virtual Reality (VR) / Virtual Environment (VE), which focus on User Experience (UX) to provide more engaging and immersive experiences, can help people grow their skills. Technology advancement is also an essential component of VR development. However, the literature needs to contain more studies on using VR as an assistive tool for skill development. This study aims to explore the impact of VR technological advancements on skill development through UX design taxonomies using a Systematic Literature Review (SLR). Skill development classification was conducted based on social, emotional, and behavioral (SEB) aspects. The selected studies that met the eligibility selection criteria were examined and synthesized. The study's findings highlight the necessity of technology development for VR technology to accomplish UX for skill development, allowing them to become more self-sufficient. This research can enrich researchers and VR developers, particularly software, hardware, and artificial intelligence (AI) experts. More research should be conducted on the long-term use of VR as an assistive device, particularly for those seeking skill improvement to improve their quality of life.</t>
+  </si>
+  <si>
+    <t>DISCOVER COMPUTING</t>
+  </si>
+  <si>
+    <t>Ichsan et al.</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>Systematic review on Virtual-reality technology for SEB skill development</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.lindif.2024.102605</t>
+  </si>
+  <si>
+    <t>This paper explores inequalities in adolescents' social, emotional, and behavioral skills. We examine whether skills vary by gender, parental education, immigrant background, school track-and their intersections. In two samples of German adolescents (age 14-20y</t>
+  </si>
+  <si>
+    <t>Lechner &amp; Urban</t>
+  </si>
+  <si>
+    <t>Inequalities in SEB skills by gender, SES, and migration background</t>
+  </si>
+  <si>
+    <t>open materials: https://osf.io/6c52d/?view_only=38829369699e4862a4d75a08338ae448</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3390/jintelligence10030063</t>
+  </si>
+  <si>
+    <t>Social, emotional, and behavioral (SEB) skills comprise a broad set of abilities that are essential for building and maintaining relationships, regulating emotions, selecting and pursuing goals, or exploring novel stimuli. Toward an improved SEB skill assessment, Soto and colleagues recently introduced the Behavioral, Emotional, and Social Skills Inventory (BESSI). Measuring 32 facets from 5 domains with 192 items (assessment duration: similar to 15 min), BESSI constitutes the most extensive SEB inventory to date. However, so far, BESSI exists only in English. In three studies, we comprehensively validated a novel German-language adaptation, BESSI-G. Moreover, we expanded evidence on BESSI in three ways by (1) assessing the psychometric properties of the 32 individual skill facets, in addition to their domain-level structure</t>
+  </si>
+  <si>
+    <t>Lechner et al.</t>
+  </si>
+  <si>
+    <t>Validation of the German version of the BESSI</t>
+  </si>
+  <si>
+    <t>OSF NOT WORKING</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feduc.2021.679561</t>
+  </si>
+  <si>
+    <t>Social, emotional, and behavioral (SEB) skills encompass a wide range of competencies related to how individuals build and maintain relationships, understand and manage emotions, pursue goals, and learn from experience. Despite near-consensus on the importance of SEB skills for success in life, there are numerous frameworks that simultaneously converge and diverge in how they define and measure SEB skills. In this article, we discuss our integrative model encompassing five broad skill domains: Self-Management, Innovation, Social Engagement, Cooperation, and Emotional Resilience Skills (Soto et al., 2021a). Our model defines SEB skills as skills (i.e., what someone is capable of doing) and not traits (i.e., what someone tends to do). Using this definition and model as a foundation, we argue for the importance of investigating SEB skill development during adolescence, a period where SEB skills may be both particularly amenable to change and particularly predictive of life outcomes. In particular, we highlight how SEB skills allow adolescents to take advantage of the new opportunities afforded to them as they make major cognitive and social transitions.</t>
+  </si>
+  <si>
+    <t>FRONTIERS IN EDUCATION</t>
+  </si>
+  <si>
+    <t>Napolitano et al.</t>
+  </si>
+  <si>
+    <t>Integrative SEB model and its developmental importance in adolescence</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1177/08902070251328046</t>
+  </si>
+  <si>
+    <t>Evidence across the social sciences suggests the importance of social, emotional, and behavioral (SEB) skills for a wide variety of youth outcomes. However, most of this work is cross-sectional. We know little about how patterns of change in adolescents' SEB skills may be related to commensurate patterns of change in important outcomes across an academic year. Drawing from a sample of American secondary school students (N = 942), this longitudinal study employs latent change score models to fill that gap. We report four key findings. We find that (1) a short version of the Behavioral, Emotional, and Social Skills Inventory (BESSI) is psychometrically suitable for longitudinal analyses. We further find that (2) SEB skills are highly stable, on average, but also (3) characterized by significant between-person variation in change. Centrally, we find that (4) positive changes in SEB skills are related to changes in academic engagement, friendship quality, anxiety, depression, life satisfaction, as well as other measures of social and emotional competencies. Taken together, the results suggest that SEB skills are malleable, but future work is needed to identify patterns of change and develop and test targeted interventions.</t>
+  </si>
+  <si>
+    <t>EUROPEAN JOURNAL OF PERSONALITY</t>
+  </si>
+  <si>
+    <t>Longitudinal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secondary school </t>
+  </si>
+  <si>
+    <t>Longitudinal changes in SEB skills and outcomes</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1002/jad.12486</t>
+  </si>
+  <si>
+    <t>Introduction: Transitioning from school to higher education or work is a pivotal moment in a student's life, requiring life-changing decisions. During this period, students who have acquired a wide range of Social, Emotional, and Behavioral (SEB) skills may feel more confident regarding their capacity to adapt positively to future challenges and difficulties. Our study aimed to test whether five SEB skills domains (self-management, innovation, social engagement, cooperation, and emotional resilience skills) were associated with four career adaptability resources (i.e., concern, control, curiosity, and confidence). Methods: A cross-sectional study was conducted on 350 Italian students (143 boys</t>
+  </si>
+  <si>
+    <t>JOURNAL OF ADOLESCENCE</t>
+  </si>
+  <si>
+    <t>Pellegrino et al.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Associations between SEB skills and career adaptability </t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1177/10731911231225197</t>
+  </si>
+  <si>
+    <t>Social, emotional, and behavioral (SEB) skills encompass a broad range of interpersonal and intrapersonal abilities that are crucial for establishing and maintaining relationships, managing emotions, setting and pursuing goals, and exploring new learning opportunities. To address the lack of consensus regarding terminology, definition, and assessment of SEB skills, Soto et al. developed the Behavioral, Emotional, and Social Skills Inventory (BESSI), which consists of 192 items, 32 facets, and 5 domains. The objective of the current study was to adapt the BESSI to Spanish (referred to as BESSI-Sp) and enhance the overall understanding of the BESSI framework. A sample of 303 people was employed with a mean age of 30.35 years (SD = 14.73), ranging from 18 to 85 years. The results indicate that the BESSI-Sp demonstrates strong psychometric properties. Its facet- and domain-level structure aligns with the theoretical expectations and closely resembles the English-language source version. The facets exhibit high reliability (mean omega = .89), and the scores demonstrate adequate stability after 3 to 4 weeks (mean rICC = .77). The BESSI-Sp also displays evidence of convergent validity and integrates well with the Big Five framework, providing incremental validity for various outcomes. We discuss the implications of these findings for the assessment of SEB skills and future research in this field.</t>
+  </si>
+  <si>
+    <t>ASSESSMENT</t>
+  </si>
+  <si>
+    <t>Postigo et al.</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Validation of the Spanish version of the BESSI</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1177/08902070241309960</t>
+  </si>
+  <si>
+    <t>Personality traits and social, emotional, and behavioral (SEB) skills are closely related but incrementally predict life outcomes. This implies that although tightly connected, what a person tends to do (personality traits) and what they are capable of doing (skills) are not always perfectly aligned. In this study, we investigated whether matches and mismatches between traits and skills predict important life outcomes. We studied a diverse sample of high school students (N = 840) who self-reported their Big Five personality traits, five SEB skill domains, and an array of academic, social, and emotional outcomes. Using response surface analysis, we found that matching trait/skill levels did not confer a unique benefit for adolescents over the additive effects of traits and skills. In contrast, we found that trait/skill mismatches predicted outcomes, and in some cases, adolescents with mismatching trait/skills had the best and worst outcomes. Specifically, youth with higher skill levels relative to their traits reported better outcomes, and those with lower skills relative to their traits reported worse outcomes. Our findings provide insights into functioning that are missed by solely focusing on direct effects and show that SEB skills can enhance youth's personality strengths and buffer against shortcomings.</t>
+  </si>
+  <si>
+    <t>Ringwald et al.</t>
+  </si>
+  <si>
+    <t>Trait–skill (mis)matches and implications for youth outcomes</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1177/10731911241256434</t>
+  </si>
+  <si>
+    <t>Social, emotional, and behavioral (SEB) skills matter for individuals' well-being and success. The behavioral, emotional, and social skills inventory (BESSI) uses 192 items to assess 32 specific SEB skills across five broad skill domains. This research developed three short forms of the BESSI-192 and explored their measurement properties, predictive validity, and cross-cultural comparability. We found that BESSI-96, BESSI-45, and BESSI-20 largely captured the psychological content of the BESSI-192 measure, retained a robust multidimensional structure, and demonstrated adequate reliability. At the domain and facet level, the BESSI short forms showed patterns of associations with external criteria that were similar to the BESSI-192 and preserved most of the BESSI-192's predictive power. The BESSI short forms also demonstrated full or partial measurement invariance between the primarily U.S.-based and German adult samples. We conclude by discussing contexts in which the short forms may be useful for researchers and practitioners.</t>
+  </si>
+  <si>
+    <t>Sewell et al.</t>
+  </si>
+  <si>
+    <t>Germany, United States</t>
+  </si>
+  <si>
+    <t>Secondary school, Yound adults, Adults</t>
+  </si>
+  <si>
+    <t>Development and validation of short BESSI forms</t>
+  </si>
+  <si>
+    <t>Should we add cor for shorter scales although same data?</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1111/jora.12830</t>
+  </si>
+  <si>
+    <t>The disruptions to community functioning caused by the COVID-19 pandemic spurred individuals to action. This empirical study investigated the social, emotional, and behavioral (SEB) skill antecedents to college students' volunteering during the COVID-19 pandemic (N = 248, Mage = 20.6). We assessed eight SEB skills at the onset of a volunteering program, and students' volunteer hours were assessed 10-weeks later. Approximately 41.5\% of the sample did not complete any volunteer hours. Higher levels of perspective taking skill, abstract thinking skill, and stress regulation were associated with more time spent volunteering. These results suggest that strength in particular SEB skills can prospectively predict prosocial civic behaviors.</t>
+  </si>
+  <si>
+    <t>JOURNAL OF RESEARCH ON ADOLESCENCE</t>
+  </si>
+  <si>
+    <t>SEB skill predictors of volunteering during COVID-19</t>
+  </si>
+  <si>
+    <t>Some variables excluded (ethnicity…)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/fpsyg.2025.1653072</t>
+  </si>
+  <si>
+    <t>The present study tested a comprehensive model in which five social, emotional, and behavioral (SEB) skill domains (self-management, social engagement, cooperation, emotional resilience, and innovation</t>
+  </si>
+  <si>
+    <t>Frontiers in Psychology</t>
+  </si>
+  <si>
+    <t>Sharabi et al.</t>
+  </si>
+  <si>
+    <t>Israel, Italy, Spain</t>
+  </si>
+  <si>
+    <t>Association between SEB skills and university student outcomes</t>
+  </si>
+  <si>
+    <t>bessi20</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jrp.2023.104382</t>
+  </si>
+  <si>
+    <t>The present research examined relations between social, emotional, and behavioral (SEB) skills, personality traits, and academic success in a sample of adolescents (N = 975). Results indicated that both skills and traits robustly predicted school grades, educational aspirations, and performance on a standardized achievement test, even after accounting for demographic characteristics. Moreover, skills and traits were often interchangeable: when assessed using the same cognitive, affective, and behavioral referents, they converged strongly and did not provide incremental validity over each other for predicting most outcomes. However, skills provided some in-cremental validity beyond traits for predicting standardized test performance. Taken together, these findings highlight the importance of SEB skills and personality traits for predicting and understanding academic success.</t>
+  </si>
+  <si>
+    <t>JOURNAL OF RESEARCH IN PERSONALITY</t>
+  </si>
+  <si>
+    <t>Soto et al.</t>
+  </si>
+  <si>
+    <t>SEB skills and traits predicting academic success</t>
+  </si>
+  <si>
+    <t>These were excluded from the corTab Grade level	Ethnicity Black/African-American	Ethnicity Hispanic/Latino	Ethnicity Asian/Asian-American</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1177/19485506221127483</t>
+  </si>
+  <si>
+    <t>The present research addresses three key questions about social, emotional, and behavioral (SEB) skills. First, how do SEB skills relate with the Big Five traits and Collaborative for Academic, Social, and Emotional Learning (CASEL) core competencies? Second, how do SEB skills relate with consequential outcomes in adolescence? Third, do SEB skills provide incremental validity beyond personality traits? Results from a diverse sample of high school students (N = 897) indicate that SEB skills converge with the Big Five traits and CASEL competencies in expected and conceptually meaningful ways. Analyses of self-reported and school-reported outcomes extend SEB skills' nomological network by showing that they predict academic achievement and engagement, occupational interests, social relationships, civic engagement, and well-being. Finally, tests of incremental validity indicate that SEB skills provide unique information beyond personality traits and that this information matters for predicting outcomes during adolescence. These findings advance our understanding of the nature, correlates, and consequences of SEB skills.</t>
+  </si>
+  <si>
+    <t>SOCIAL PSYCHOLOGICAL AND PERSONALITY SCIENCE</t>
+  </si>
+  <si>
+    <t>Associations between SEB skills and multiple adolescents'outcomes</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1037/pspp0000401</t>
+  </si>
+  <si>
+    <t>People differ in their social, emotional, and behavioral (SEB) skills: their capacities to maintain social relationships, regulate emotions, and manage goal- and learning-directed behaviors. In five studies using data from seven independent samples (N = 6,309), we address three key questions about the nature, structure, assessment, and outcomes of SEB skills. First, how can SEB skills be defined and distinguished from other kinds of psychological constructs, such as personality traits? We propose that SEB skills represent how someone is capable of thinking, feeling, and behaving when the situation calls for it, whereas traits represent how someone tends to think, feel, and behave averaged across situations. Second, how can specific SEB skills be organized within broader domains? We find that many skill facets can be organized within five major domains representing Social Engagement, Cooperation, Self-Management, Emotional Resilience, and Innovation Skills. Third, how should SEB skills be measured? We develop and validate the Behavioral, Emotional, and Social Skills Inventory (BESSI) to measure individuals' capacity to enact specific behaviors representing 32 skill facets. We then use the BESSI to investigate the nomological network of SEB skills. We show that both skill domains and facets converge in conceptually meaningful ways with socioemotional competencies, character and developmental strengths, and personality traits, and predict consequential outcomes including academic achievement and engagement, occupational interests, social relationships, and well-being. We believe that this work provides the most comprehensive model currently available for conceptualizing SEB skills, as well as the most psychometrically robust tool available for assessing them.</t>
+  </si>
+  <si>
+    <t>JOURNAL OF PERSONALITY AND SOCIAL PSYCHOLOGY</t>
+  </si>
+  <si>
+    <t>Secondary school, Young adults, Adults</t>
+  </si>
+  <si>
+    <t>Validation of the original BESSI</t>
+  </si>
+  <si>
     <t>https://doi.org/10.20453/rnp.v87i1.5046</t>
   </si>
   <si>
@@ -64,162 +557,27 @@
     <t>Peru</t>
   </si>
   <si>
-    <t>school_age</t>
-  </si>
-  <si>
-    <t>not_clinical</t>
-  </si>
-  <si>
-    <t>bessi45</t>
-  </si>
-  <si>
-    <t>short</t>
+    <t xml:space="preserve">Validation of the peruvian version of the Resilience Subscale of the BESSI </t>
   </si>
   <si>
     <t>only one skill assessed and nothing else</t>
   </si>
   <si>
-    <t>https://doi.org/10.1177/08902070241309960</t>
-  </si>
-  <si>
-    <t>Personality traits and social, emotional, and behavioral (SEB) skills are closely related but incrementally predict life outcomes. This implies that although tightly connected, what a person tends to do (personality traits) and what they are capable of doing (skills) are not always perfectly aligned. In this study, we investigated whether matches and mismatches between traits and skills predict important life outcomes. We studied a diverse sample of high school students (N = 840) who self-reported their Big Five personality traits, five SEB skill domains, and an array of academic, social, and emotional outcomes. Using response surface analysis, we found that matching trait/skill levels did not confer a unique benefit for adolescents over the additive effects of traits and skills. In contrast, we found that trait/skill mismatches predicted outcomes, and in some cases, adolescents with mismatching trait/skills had the best and worst outcomes. Specifically, youth with higher skill levels relative to their traits reported better outcomes, and those with lower skills relative to their traits reported worse outcomes. Our findings provide insights into functioning that are missed by solely focusing on direct effects and show that SEB skills can enhance youth's personality strengths and buffer against shortcomings.</t>
-  </si>
-  <si>
-    <t>EUROPEAN JOURNAL OF PERSONALITY</t>
-  </si>
-  <si>
-    <t>Ringwald et al.</t>
-  </si>
-  <si>
-    <t>United States</t>
-  </si>
-  <si>
     <t>https://doi.org/10.1080/00223891.2024.2444447</t>
   </si>
   <si>
     <t>Recent research has examined similarities and differences between traits and skills. It may be the case that traits and skills can be measured interchangeably with one providing little to no incremental validity over the other. However, methodological limitations constrain our ability to draw firm conclusions. Work in this area thus far has only examined self-reports and single-stimulus Likert items. We carried out two studies to try to determine the extent to which methodology influences observed trait-skill similarity. In Study 1, we collected both self- and observer-reports of traits and skills, and in Study 2, we used both Likert and forced choice items. We examined whether trait-skill similarity in scores and validity evidence varied according to rater and item type. Our findings suggest that trait-skill similarity is unaffected by rater but is affected by item type</t>
   </si>
   <si>
-    <t>JOURNAL OF PERSONALITY ASSESSMENT</t>
-  </si>
-  <si>
     <t>Walton et al.</t>
   </si>
   <si>
+    <t>Assessment challenges in differetiating skills vs traits</t>
+  </si>
+  <si>
     <t>Adapted skill-trait measures</t>
   </si>
   <si>
-    <t>https://doi.org/10.1016/j.lindif.2024.102605</t>
-  </si>
-  <si>
-    <t>This paper explores inequalities in adolescents' social, emotional, and behavioral skills. We examine whether skills vary by gender, parental education, immigrant background, school track-and their intersections. In two samples of German adolescents (age 14-20y</t>
-  </si>
-  <si>
-    <t>LEARNING AND INDIVIDUAL DIFFERENCES</t>
-  </si>
-  <si>
-    <t>Lechner &amp; Urban</t>
-  </si>
-  <si>
-    <t>Germany</t>
-  </si>
-  <si>
-    <t>open materials: https://osf.io/6c52d/?view_only=38829369699e4862a4d75a08338ae448</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.lindif.2024.102581</t>
-  </si>
-  <si>
-    <t>Social, emotional, and behavioral (SEB) skills are key factors for academic and non-academic outcomes, but no previous studies deepened SEB skills of students with specific learning disabilities (SLD). We used the Behavioral, Emotional, and Social Skills Inventory (BESSI) to systematically investigate i) differences in social engagement, self-management, innovation, emotional resilience, and cooperation skills and ii) the interaction effect between skills and group on academic achievement and life satisfaction. In a sample of 2965 students (1589 females, M = 15.5 years, SD = 2.0), 359 of whom reported a SLD, we found differences in self-management (d = -0.28), innovation (d = -0.25), and social engagement (d = -0.19) skills. Furthermore, higher SEB skills do not guarantee higher academic achievement in the SLD group, while their role is similar in the two groups for life satisfaction. Overall, students with SLD may benefit from interventions to improve knowledge and use of SEB skills.</t>
-  </si>
-  <si>
-    <t>Feraco et al.</t>
-  </si>
-  <si>
-    <t>Italy</t>
-  </si>
-  <si>
-    <t>bessi192</t>
-  </si>
-  <si>
-    <t>long</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.paid.2024.112870</t>
-  </si>
-  <si>
-    <t>Past research has demonstrated that university students with a stronger sense of purpose tend to fare better than their peers. However, work is needed to investigate the mechanisms and skills that may underlie these associations. The current studies employed two university student samples (total n = 412) and comprehensively investigated associations between sense of purpose and social-emotional-behavioral skills, using multiple purpose measures. Associations were relatively similar across measures and samples, and results suggested that sense of purpose was most robustly positively associated with self-management skills. Sense of purpose also was associated with better student wellbeing (life satisfaction, college satisfaction, and student connectedness), though it was inconsistently associated with reported likelihood of degree completion. Sense of purpose largely remained a significant correlate of student wellbeing, even when accounting for SEB skill domains, although some associations between purpose and wellbeing were reduced in magnitude.</t>
-  </si>
-  <si>
-    <t>PERSONALITY AND INDIVIDUAL DIFFERENCES</t>
-  </si>
-  <si>
-    <t>Beatty et al.</t>
-  </si>
-  <si>
-    <t>young_adult</t>
-  </si>
-  <si>
-    <t>bessi96</t>
-  </si>
-  <si>
-    <t>Only cor between skills and outcomes available</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1525/collabra.120531</t>
-  </si>
-  <si>
-    <t>The current study sought to extend Soto et al. (2022)'s results on social, emotional, and behavioral (SEB) skills to a work setting and answer three key questions. First, do SEB skills predict consequential work-related outcomes? Second, do SEB skills provide incremental validity over the Big Five personality traits in predicting the outcomes? Third, is the joint effect of SEB skills and traits additive or multiplicative? Results from a sample of real estate agents (N N = 2,992) in China extend the criterion space of SEB skills by showing self-concepts of these skills are related to self-reported work outcomes such as citizenship behaviors and job satisfaction in a conceptually meaningful way. Further analyses show that these skill-outcome relationships remain robust after accounting for effects of traits, indicating SEB skills' incremental validity beyond traits in predicting outcomes. Finally, comparisons between additive and multiplicative models show support for the former because the interaction effects of SEB skills and traits provide little meaningful information beyond the additive models. Based on these findings, we discuss the implications for the SEB skills literature and practice.</t>
-  </si>
-  <si>
-    <t>COLLABRA-PSYCHOLOGY</t>
-  </si>
-  <si>
-    <t>Chen et al.</t>
-  </si>
-  <si>
-    <t>China</t>
-  </si>
-  <si>
-    <t>adult</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1177/10731911241256434</t>
-  </si>
-  <si>
-    <t>Social, emotional, and behavioral (SEB) skills matter for individuals' well-being and success. The behavioral, emotional, and social skills inventory (BESSI) uses 192 items to assess 32 specific SEB skills across five broad skill domains. This research developed three short forms of the BESSI-192 and explored their measurement properties, predictive validity, and cross-cultural comparability. We found that BESSI-96, BESSI-45, and BESSI-20 largely captured the psychological content of the BESSI-192 measure, retained a robust multidimensional structure, and demonstrated adequate reliability. At the domain and facet level, the BESSI short forms showed patterns of associations with external criteria that were similar to the BESSI-192 and preserved most of the BESSI-192's predictive power. The BESSI short forms also demonstrated full or partial measurement invariance between the primarily U.S.-based and German adult samples. We conclude by discussing contexts in which the short forms may be useful for researchers and practitioners.</t>
-  </si>
-  <si>
-    <t>ASSESSMENT</t>
-  </si>
-  <si>
-    <t>Sewell et al.</t>
-  </si>
-  <si>
-    <t>Should we add cor for shorter scales although same data?</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1080/00223891.2024.2335912</t>
-  </si>
-  <si>
-    <t>The importance of social, emotional, and behavioral (SEB) skills is recognized worldwide, but their measurement has always been a challenge. The BESSI measures 32 SEB skills, divided into five domains (social engagement, cooperation, self-management, emotional resilience, and innovation), but its validity must be expanded to new languages and contexts. Across two studies (N1 = 990, N2= 824) we developed the Italian version of the BESSI, provided further support for its convergent and discriminant validity with the Big Five, and expanded its nomological network to procrastination, self-efficacy, and emotion regulation. The BESSI-I showed excellent internal reliability and satisfactory fit indices at the facet, domain, and overarching framework level. We also confirmed the correlations between the SEB skills and the Big Five personality traits and found meaningful correlations with the selected external outcomes. Overall, we confirm that the BESSI-I is a valid and useful instrument to assess SEB skills for research and clinical purposes.</t>
-  </si>
-  <si>
-    <t>includes school age and adults</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1177/10731911231225197</t>
-  </si>
-  <si>
-    <t>Social, emotional, and behavioral (SEB) skills encompass a broad range of interpersonal and intrapersonal abilities that are crucial for establishing and maintaining relationships, managing emotions, setting and pursuing goals, and exploring new learning opportunities. To address the lack of consensus regarding terminology, definition, and assessment of SEB skills, Soto et al. developed the Behavioral, Emotional, and Social Skills Inventory (BESSI), which consists of 192 items, 32 facets, and 5 domains. The objective of the current study was to adapt the BESSI to Spanish (referred to as BESSI-Sp) and enhance the overall understanding of the BESSI framework. A sample of 303 people was employed with a mean age of 30.35 years (SD = 14.73), ranging from 18 to 85 years. The results indicate that the BESSI-Sp demonstrates strong psychometric properties. Its facet- and domain-level structure aligns with the theoretical expectations and closely resembles the English-language source version. The facets exhibit high reliability (mean omega = .89), and the scores demonstrate adequate stability after 3 to 4 weeks (mean rICC = .77). The BESSI-Sp also displays evidence of convergent validity and integrates well with the Big Five framework, providing incremental validity for various outcomes. We discuss the implications of these findings for the assessment of SEB skills and future research in this field.</t>
-  </si>
-  <si>
-    <t>Postigo et al.</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
     <t>https://doi.org/10.1371/journal.pone.0296484</t>
   </si>
   <si>
@@ -232,359 +590,17 @@
     <t>Yoon et al.</t>
   </si>
   <si>
+    <t>SEB skills and their incremental validity for academic achievement beyond personality traits</t>
+  </si>
+  <si>
     <t>Only one facet per domain (not real domain)</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3390/jintelligence11060118</t>
-  </si>
-  <si>
-    <t>Individuals use social, emotional, and behavioral (SEB) skills to build and maintain social relationships, regulate emotions, and manage goal-directed behaviors. A promising integrative framework of SEB skills was recently proposed, showing that they matter for positive outcomes during adolescence. Nothing is known about how and whether they differ between 12 and 19 years old and whether such differences depend on gender (males or females). Uncovering their age trajectories is fundamental because SEB skills are highly needed during this period of life. Educators, psychologists, and policymakers need to understand when, why, and how interventions concerning SEB skills should be proposed, potentially considering male and female profiles. To cover this gap, we cross-sectionally analyzed data from 4106 participants (2215 females, 12-19 years old). We highlighted age and gender differences in the five domains of SEB skills (self-management, innovation, cooperation, social engagement, and emotional resilience). Our results show that each SEB skill follows a specific age trend: emotional resilience and cooperation skills increase naturally between 12 and 19 years old, while innovation, social engagement, and self-management skills decline, especially between 12 and 16 years old, and grow later. The trajectories of self-management, social engagement, and emotional resilience skills also differ between males and females. Importantly, we detected declines in SEB skills (especially for social engagement and innovation skills) that can inform policies and interventions to sustain SEB skills in youths to favor their well-being and success in this crucial period.</t>
-  </si>
-  <si>
-    <t>JOURNAL OF INTELLIGENCE</t>
-  </si>
-  <si>
-    <t>Feraco &amp; Meneghetti</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.jrp.2023.104382</t>
-  </si>
-  <si>
-    <t>The present research examined relations between social, emotional, and behavioral (SEB) skills, personality traits, and academic success in a sample of adolescents (N = 975). Results indicated that both skills and traits robustly predicted school grades, educational aspirations, and performance on a standardized achievement test, even after accounting for demographic characteristics. Moreover, skills and traits were often interchangeable: when assessed using the same cognitive, affective, and behavioral referents, they converged strongly and did not provide incremental validity over each other for predicting most outcomes. However, skills provided some in-cremental validity beyond traits for predicting standardized test performance. Taken together, these findings highlight the importance of SEB skills and personality traits for predicting and understanding academic success.</t>
-  </si>
-  <si>
-    <t>JOURNAL OF RESEARCH IN PERSONALITY</t>
-  </si>
-  <si>
-    <t>Soto et al.</t>
-  </si>
-  <si>
-    <t>bessi20</t>
-  </si>
-  <si>
-    <t>These were excluded from the corTab Grade level	Ethnicity Black/African-American	Ethnicity Hispanic/Latino	Ethnicity Asian/Asian-American</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1111/jora.12830</t>
-  </si>
-  <si>
-    <t>The disruptions to community functioning caused by the COVID-19 pandemic spurred individuals to action. This empirical study investigated the social, emotional, and behavioral (SEB) skill antecedents to college students' volunteering during the COVID-19 pandemic (N = 248, Mage = 20.6). We assessed eight SEB skills at the onset of a volunteering program, and students' volunteer hours were assessed 10-weeks later. Approximately 41.5\% of the sample did not complete any volunteer hours. Higher levels of perspective taking skill, abstract thinking skill, and stress regulation were associated with more time spent volunteering. These results suggest that strength in particular SEB skills can prospectively predict prosocial civic behaviors.</t>
-  </si>
-  <si>
-    <t>JOURNAL OF RESEARCH ON ADOLESCENCE</t>
-  </si>
-  <si>
-    <t>Some variables excluded (ethnicity…)</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1177/19485506221127483</t>
-  </si>
-  <si>
-    <t>The present research addresses three key questions about social, emotional, and behavioral (SEB) skills. First, how do SEB skills relate with the Big Five traits and Collaborative for Academic, Social, and Emotional Learning (CASEL) core competencies? Second, how do SEB skills relate with consequential outcomes in adolescence? Third, do SEB skills provide incremental validity beyond personality traits? Results from a diverse sample of high school students (N = 897) indicate that SEB skills converge with the Big Five traits and CASEL competencies in expected and conceptually meaningful ways. Analyses of self-reported and school-reported outcomes extend SEB skills' nomological network by showing that they predict academic achievement and engagement, occupational interests, social relationships, civic engagement, and well-being. Finally, tests of incremental validity indicate that SEB skills provide unique information beyond personality traits and that this information matters for predicting outcomes during adolescence. These findings advance our understanding of the nature, correlates, and consequences of SEB skills.</t>
-  </si>
-  <si>
-    <t>SOCIAL PSYCHOLOGICAL AND PERSONALITY SCIENCE</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3390/jintelligence10030048</t>
-  </si>
-  <si>
-    <t>Social skills are of key importance in everyday and work life. However, the way in which they are typically assessed via self-report questionnaires has one potential downside</t>
-  </si>
-  <si>
-    <t>Breil et al.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3390/jintelligence10030063</t>
-  </si>
-  <si>
-    <t>Social, emotional, and behavioral (SEB) skills comprise a broad set of abilities that are essential for building and maintaining relationships, regulating emotions, selecting and pursuing goals, or exploring novel stimuli. Toward an improved SEB skill assessment, Soto and colleagues recently introduced the Behavioral, Emotional, and Social Skills Inventory (BESSI). Measuring 32 facets from 5 domains with 192 items (assessment duration: similar to 15 min), BESSI constitutes the most extensive SEB inventory to date. However, so far, BESSI exists only in English. In three studies, we comprehensively validated a novel German-language adaptation, BESSI-G. Moreover, we expanded evidence on BESSI in three ways by (1) assessing the psychometric properties of the 32 individual skill facets, in addition to their domain-level structure</t>
-  </si>
-  <si>
-    <t>Lechner et al.</t>
-  </si>
-  <si>
-    <t>OSF NOT WORKING</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1037/pspp0000401</t>
-  </si>
-  <si>
-    <t>People differ in their social, emotional, and behavioral (SEB) skills: their capacities to maintain social relationships, regulate emotions, and manage goal- and learning-directed behaviors. In five studies using data from seven independent samples (N = 6,309), we address three key questions about the nature, structure, assessment, and outcomes of SEB skills. First, how can SEB skills be defined and distinguished from other kinds of psychological constructs, such as personality traits? We propose that SEB skills represent how someone is capable of thinking, feeling, and behaving when the situation calls for it, whereas traits represent how someone tends to think, feel, and behave averaged across situations. Second, how can specific SEB skills be organized within broader domains? We find that many skill facets can be organized within five major domains representing Social Engagement, Cooperation, Self-Management, Emotional Resilience, and Innovation Skills. Third, how should SEB skills be measured? We develop and validate the Behavioral, Emotional, and Social Skills Inventory (BESSI) to measure individuals' capacity to enact specific behaviors representing 32 skill facets. We then use the BESSI to investigate the nomological network of SEB skills. We show that both skill domains and facets converge in conceptually meaningful ways with socioemotional competencies, character and developmental strengths, and personality traits, and predict consequential outcomes including academic achievement and engagement, occupational interests, social relationships, and well-being. We believe that this work provides the most comprehensive model currently available for conceptualizing SEB skills, as well as the most psychometrically robust tool available for assessing them.</t>
-  </si>
-  <si>
-    <t>JOURNAL OF PERSONALITY AND SOCIAL PSYCHOLOGY</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feduc.2021.679561</t>
-  </si>
-  <si>
-    <t>Social, emotional, and behavioral (SEB) skills encompass a wide range of competencies related to how individuals build and maintain relationships, understand and manage emotions, pursue goals, and learn from experience. Despite near-consensus on the importance of SEB skills for success in life, there are numerous frameworks that simultaneously converge and diverge in how they define and measure SEB skills. In this article, we discuss our integrative model encompassing five broad skill domains: Self-Management, Innovation, Social Engagement, Cooperation, and Emotional Resilience Skills (Soto et al., 2021a). Our model defines SEB skills as skills (i.e., what someone is capable of doing) and not traits (i.e., what someone tends to do). Using this definition and model as a foundation, we argue for the importance of investigating SEB skill development during adolescence, a period where SEB skills may be both particularly amenable to change and particularly predictive of life outcomes. In particular, we highlight how SEB skills allow adolescents to take advantage of the new opportunities afforded to them as they make major cognitive and social transitions.</t>
-  </si>
-  <si>
-    <t>FRONTIERS IN EDUCATION</t>
-  </si>
-  <si>
-    <t>Napolitano et al.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.paid.2025.113200</t>
-  </si>
-  <si>
-    <t>Although research suggests that most people want to change their personality traits, previous studies have neither explored whether individuals also desire to change the social, emotional, and behavioral (SEB) skills linked to those traits, nor whether people have different beliefs about the malleability of skills vs. traits. In the present within-person experiment, 264 young adults from the US and Italy rated their desire to change each of the Big Five personality traits and the corresponding domains of SEB skills. They also rated their beliefs about the feasibility, motivation, and impact of making these changes. Results showed that participants reported similar or higher scores for skills, compared to traits, across all measured outcomes. Specifically, scores for social engagement and self-management skills were consistently higher than those for extraversion and conscientiousness. These findings indicate that people believe it to be more desirable-and more feasible-to change some SEB skills than the corresponding personality traits.</t>
-  </si>
-  <si>
-    <t>Change goals</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1177/08902070251328046</t>
-  </si>
-  <si>
-    <t>Evidence across the social sciences suggests the importance of social, emotional, and behavioral (SEB) skills for a wide variety of youth outcomes. However, most of this work is cross-sectional. We know little about how patterns of change in adolescents' SEB skills may be related to commensurate patterns of change in important outcomes across an academic year. Drawing from a sample of American secondary school students (N = 942), this longitudinal study employs latent change score models to fill that gap. We report four key findings. We find that (1) a short version of the Behavioral, Emotional, and Social Skills Inventory (BESSI) is psychometrically suitable for longitudinal analyses. We further find that (2) SEB skills are highly stable, on average, but also (3) characterized by significant between-person variation in change. Centrally, we find that (4) positive changes in SEB skills are related to changes in academic engagement, friendship quality, anxiety, depression, life satisfaction, as well as other measures of social and emotional competencies. Taken together, the results suggest that SEB skills are malleable, but future work is needed to identify patterns of change and develop and test targeted interventions.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1177/20965311251319355</t>
-  </si>
-  <si>
-    <t>Purpose This review paper addresses three major challenges hindering progress in the field of social-emotional learning in education.Design/Approach/Methods We first discuss how social-emotional skills could be conceptualized, contrasting identity versus self-efficacy approaches. Second, we argue to develop more objective assessments of social-emotional skills and their development, as a supplement of currently and frequently used self- and informant descriptions relying on Likert-based scales. Third and finally, we discuss recurrent issues that are raised when debating the implementation of social-emotional skill learning in the classroom.Findings The review suggests that, at this point in time, both self-efficacy and identity conceptualizations of social-emotional skills are valuable approaches. Future research will need to explore which conceptualization for which skills demonstrates the best predictive validity, taking into account the nature of outcomes and contexts. The desired characteristics of more objective social-emotional skill measures are defined, and we encourage to examine how these overlap with self-reports using construct maps. Finally, we underscore the importance of having a comprehensive and evidence-informed taxonomy of social-emotional skills to guide the debate on the inclusion of social-emotional skill learning in curricula and its implementation in the classroom.Originality/Value This short review is primarily written for practitioners and policymakers to give a quick and accessible update on the key challenges in social-emotional learning today. The review should trigger more in-depth reading on the topic, but also support readers to understand current problems and help them dealing with questions and potential objections that might be raised by different stakeholders.</t>
-  </si>
-  <si>
-    <t>ECNU REVIEW OF EDUCATION</t>
-  </si>
-  <si>
-    <t>De Fruyt et al.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1002/jad.12486</t>
-  </si>
-  <si>
-    <t>Introduction: Transitioning from school to higher education or work is a pivotal moment in a student's life, requiring life-changing decisions. During this period, students who have acquired a wide range of Social, Emotional, and Behavioral (SEB) skills may feel more confident regarding their capacity to adapt positively to future challenges and difficulties. Our study aimed to test whether five SEB skills domains (self-management, innovation, social engagement, cooperation, and emotional resilience skills) were associated with four career adaptability resources (i.e., concern, control, curiosity, and confidence). Methods: A cross-sectional study was conducted on 350 Italian students (143 boys</t>
-  </si>
-  <si>
-    <t>JOURNAL OF ADOLESCENCE</t>
-  </si>
-  <si>
-    <t>Pellegrino et al.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1080/13504622.2025.2459323</t>
-  </si>
-  <si>
-    <t>Following indications from international organizations, this study tests the associations between the five domains of social, emotional, and behavioral (SEB) skills (self-management, innovation, social engagement, cooperation, and emotional resilience) and two key antecedents of proenvironmental behavior, namely nature connectedness and self-perceived action competence for sustainability, in a sample of 702 students aged between 12 and 20 years (M = 16.18, SD = 2.15</t>
-  </si>
-  <si>
-    <t>ENVIRONMENTAL EDUCATION RESEARCH</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s11218-025-10095-9</t>
-  </si>
-  <si>
-    <t>Social, emotional, and behavioral (SEB) skills- also known under labels like soft skills, 21st century skills, or social-emotional skills- are considered key factors for students' success, well-being, and social relationships, among others. However, literature on the topic relied on different frameworks and questionable measurement methods. Additionally, they usually did not integrate skills into classical self-regulated learning (SRL) frameworks. To overcome these limitations, we adopted the new integrative SEB framework and measured SEB skills, along with five SRL factors (academic self-efficacy, SRL strategies, mastery learning goals, growth mindset, and achievement emotions) and three outcomes (i.e., self-reported academic achievement, peer acceptance, and life satisfaction). Participants were 5,075 Italian high school students (M = 18.23 years old</t>
-  </si>
-  <si>
-    <t>SOCIAL PSYCHOLOGY OF EDUCATION</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s10791-025-09703-1</t>
-  </si>
-  <si>
-    <t>New technologies, such as Virtual Reality (VR) / Virtual Environment (VE), which focus on User Experience (UX) to provide more engaging and immersive experiences, can help people grow their skills. Technology advancement is also an essential component of VR development. However, the literature needs to contain more studies on using VR as an assistive tool for skill development. This study aims to explore the impact of VR technological advancements on skill development through UX design taxonomies using a Systematic Literature Review (SLR). Skill development classification was conducted based on social, emotional, and behavioral (SEB) aspects. The selected studies that met the eligibility selection criteria were examined and synthesized. The study's findings highlight the necessity of technology development for VR technology to accomplish UX for skill development, allowing them to become more self-sufficient. This research can enrich researchers and VR developers, particularly software, hardware, and artificial intelligence (AI) experts. More research should be conducted on the long-term use of VR as an assistive device, particularly for those seeking skill improvement to improve their quality of life.</t>
-  </si>
-  <si>
-    <t>DISCOVER COMPUTING</t>
-  </si>
-  <si>
-    <t>Ichsan et al.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/fpsyg.2025.1653072</t>
-  </si>
-  <si>
-    <t>The present study tested a comprehensive model in which five social, emotional, and behavioral (SEB) skill domains (self-management, social engagement, cooperation, emotional resilience, and innovation</t>
-  </si>
-  <si>
-    <t>Frontiers in Psychology</t>
-  </si>
-  <si>
-    <t>Sharabi et al.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s11218-025-10079-9</t>
-  </si>
-  <si>
-    <t>In this study, we investigated perceived social-emotional competence (PSEC) among 373 Australian secondary school students in relation to parent ratings of social-emotional skills, and perceived teacher and parental autonomy support. Using bifactor exploratory structural equation modelling, we examined five dimensions of PSEC (perceived competence for assertiveness, tolerance, social regulation, emotion regulation, and emotional awareness), identifying a global factor and five specific factors. Following that, we employed structural equation modelling to investigate links between these global and specific factors and five parent-reported social-emotional skills: leadership, cultural competence, teamwork, cognitive reappraisal, and capacity for emotional reflection. Global PSEC was associated positively with all skills, whereas the specific factors were, with one exception, each associated with greater parent-rated skill in a corresponding area (e.g., assertiveness with greater leadership skill; emotion awareness with reflective skills). Addressing a second aim of the research, we tested the extent to which students’ perceptions of autonomy support from teachers and parents assessed near the start of a school term were associated with both students’ PSEC and parent-rated skills assessed at the end of the term. Autonomy-supportive parenting was positively associated with global PSEC. Autonomy-supportive teaching was associated with greater levels of two specific factors: perceived competence for assertiveness and social regulation. Together, findings hold relevance to knowledge and efforts aimed at enhancing social-emotional skills among students.</t>
-  </si>
-  <si>
-    <t>Social Psychology of Education</t>
-  </si>
-  <si>
-    <t>Collie &amp; Ryan</t>
-  </si>
-  <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>bessi_otherReport</t>
-  </si>
-  <si>
-    <t>clinical (specific learning disabilities)</t>
-  </si>
-  <si>
-    <t>Age and gender differences in SEB skills among adolescents</t>
-  </si>
-  <si>
-    <t>Main focus</t>
-  </si>
-  <si>
-    <t>SEB skills in students with learning disabilities</t>
-  </si>
-  <si>
-    <t>Associations between SEB skills and self-regulated learning factors</t>
-  </si>
-  <si>
-    <t>Systematic review on Virtual-reality technology for SEB skill development</t>
-  </si>
-  <si>
-    <t>Inequalities in SEB skills by gender, SES, and migration background</t>
-  </si>
-  <si>
-    <t>Integrative SEB model and its developmental importance in adolescence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associations between SEB skills and career adaptability </t>
-  </si>
-  <si>
-    <t>Trait–skill (mis)matches and implications for youth outcomes</t>
-  </si>
-  <si>
-    <t>Development and validation of short BESSI forms</t>
-  </si>
-  <si>
-    <t>SEB skill predictors of volunteering during COVID-19</t>
-  </si>
-  <si>
-    <t>Association between SEB skills and university student outcomes</t>
-  </si>
-  <si>
-    <t>SEB skills and traits predicting academic success</t>
-  </si>
-  <si>
-    <t>Associations between SEB skills and multiple adolescents'outcomes</t>
-  </si>
-  <si>
-    <t>Assessment challenges in differetiating skills vs traits</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Young adults</t>
-  </si>
-  <si>
-    <t>Adults</t>
-  </si>
-  <si>
-    <t>Secondary school</t>
-  </si>
-  <si>
-    <t>Cross-sectional</t>
-  </si>
-  <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>Longitudinal</t>
-  </si>
-  <si>
-    <t>Theoretical</t>
-  </si>
-  <si>
-    <t>Review</t>
-  </si>
-  <si>
-    <t>Israel, Italy, Spain</t>
-  </si>
-  <si>
-    <t>Italy, United States</t>
-  </si>
-  <si>
-    <t>Germany, Italy, Unites States</t>
-  </si>
-  <si>
-    <t>Secondary school &amp; Adults</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secondary school </t>
-  </si>
-  <si>
-    <t>Germany, United States</t>
-  </si>
-  <si>
-    <t>Secondary school, Yound adults, Adults</t>
-  </si>
-  <si>
-    <t>Secondary school, Young adults, Adults</t>
-  </si>
-  <si>
-    <t>Authors</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Study design</t>
-  </si>
-  <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>Associations between sense of purpose and SEB skills in university students</t>
-  </si>
-  <si>
-    <t>Associations between self- and observer- reports for three social skills</t>
-  </si>
-  <si>
-    <t>SEB skills and their incremental validity for job outcomes beyond personality traits</t>
-  </si>
-  <si>
-    <t>Parent-rated SEB skills and their associations with children perceived socio-emotional competence and autonomy support</t>
-  </si>
-  <si>
-    <t>Conceptual and methodological challenges in SEB skills assessment and interventions</t>
-  </si>
-  <si>
-    <t>Change goals and perceived feasibility about changing SEB skills vs traits</t>
-  </si>
-  <si>
-    <t>SEB skills links to pro-environmental attitudes and behaviors</t>
-  </si>
-  <si>
-    <t>Validation of the Italian version of the BESSI</t>
-  </si>
-  <si>
-    <t>Validation of the German version of the BESSI</t>
-  </si>
-  <si>
-    <t>Longitudinal changes in SEB skills and outcomes</t>
-  </si>
-  <si>
-    <t>Validation of the Spanish version of the BESSI</t>
-  </si>
-  <si>
-    <t>Validation of the original BESSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation of the peruvian version of the Resilience Subscale of the BESSI </t>
-  </si>
-  <si>
-    <t>SEB skills and their incremental validity for academic achievement beyond personality traits</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1043,20 +1059,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="42.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.88671875" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="101.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="101.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.88671875" customWidth="1"/>
+    <col min="16" max="16" width="36.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1067,1194 +1083,1194 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>168</v>
+        <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>169</v>
+        <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>170</v>
+        <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>171</v>
+        <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>137</v>
+        <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E2">
         <v>2025</v>
       </c>
       <c r="F2" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H2">
         <v>412</v>
       </c>
       <c r="I2" t="s">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>172</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N2" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="P2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="2" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="E3">
         <v>2022</v>
       </c>
       <c r="F3" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3">
         <v>137</v>
       </c>
       <c r="I3" t="s">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>173</v>
+        <v>33</v>
       </c>
       <c r="L3" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="O3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>2024</v>
       </c>
       <c r="F4" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H4">
         <v>2992</v>
       </c>
       <c r="I4" t="s">
-        <v>153</v>
+        <v>40</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>174</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N4" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="O4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
+        <v>47</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="E5">
         <v>2025</v>
       </c>
       <c r="F5" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="H5">
         <v>373</v>
       </c>
       <c r="I5" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>175</v>
+        <v>51</v>
       </c>
       <c r="L5" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="M5" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N5" t="s">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="O5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="2" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="E6">
         <v>2025</v>
       </c>
       <c r="F6" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E7">
         <v>2023</v>
       </c>
       <c r="F7" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>162</v>
+        <v>63</v>
       </c>
       <c r="H7">
         <v>4106</v>
       </c>
       <c r="I7" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="L7" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="M7" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="O7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="E8">
         <v>2025</v>
       </c>
       <c r="F8" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H8">
         <v>2965</v>
       </c>
       <c r="I8" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c r="L8" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="M8" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="N8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="O8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="E9">
         <v>2024</v>
       </c>
       <c r="F9" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H9">
         <v>1814</v>
       </c>
       <c r="I9" t="s">
-        <v>163</v>
+        <v>75</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>179</v>
+        <v>76</v>
       </c>
       <c r="L9" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="M9" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N9" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="O9" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="P9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="E10">
         <v>2025</v>
       </c>
       <c r="F10" t="s">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="G10" t="s">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="H10">
         <v>264</v>
       </c>
       <c r="I10" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="L10" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="M10" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="P10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="E11">
         <v>2025</v>
       </c>
       <c r="F11" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H11">
         <v>702</v>
       </c>
       <c r="I11" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>178</v>
+        <v>87</v>
       </c>
       <c r="L11" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="M11" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N11" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="O11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="E12">
         <v>2025</v>
       </c>
       <c r="F12" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G12" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H12">
         <v>5075</v>
       </c>
       <c r="I12" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="M12" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N12" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="O12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="E13">
         <v>2025</v>
       </c>
       <c r="F13" t="s">
-        <v>159</v>
+        <v>96</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>2025</v>
       </c>
       <c r="F14" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H14">
         <v>3162</v>
       </c>
       <c r="I14" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="M14" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="P14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="E15">
         <v>2022</v>
       </c>
       <c r="F15" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H15">
         <v>1164</v>
       </c>
       <c r="I15" t="s">
-        <v>153</v>
+        <v>40</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>180</v>
+        <v>106</v>
       </c>
       <c r="M15" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N15" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="O15" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="P15" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E16">
         <v>2021</v>
       </c>
       <c r="F16" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E17">
         <v>2025</v>
       </c>
       <c r="F17" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="G17" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H17">
         <v>942</v>
       </c>
       <c r="I17" t="s">
-        <v>164</v>
+        <v>117</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B18" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E18">
         <v>2025</v>
       </c>
       <c r="F18" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G18" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H18">
         <v>350</v>
       </c>
       <c r="I18" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="L18" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="M18" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N18" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="O18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="2" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="E19">
         <v>2024</v>
       </c>
       <c r="F19" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G19" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="H19">
         <v>303</v>
       </c>
       <c r="I19" t="s">
-        <v>153</v>
+        <v>40</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="L19" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M19" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N19" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="O19" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="P19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="E20">
         <v>2025</v>
       </c>
       <c r="F20" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H20">
         <v>840</v>
       </c>
       <c r="I20" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="L20" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="M20" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N20" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="O20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="2" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>57</v>
+        <v>136</v>
       </c>
       <c r="E21">
         <v>2024</v>
       </c>
       <c r="F21" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G21" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="H21">
         <v>2792</v>
       </c>
       <c r="I21" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="P21" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>57</v>
+        <v>136</v>
       </c>
       <c r="E22">
         <v>2023</v>
       </c>
       <c r="F22" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="G22" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H22">
         <v>248</v>
       </c>
       <c r="I22" t="s">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="J22" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="L22" t="s">
+        <v>23</v>
+      </c>
+      <c r="M22" t="s">
+        <v>24</v>
+      </c>
+      <c r="N22" t="s">
+        <v>34</v>
+      </c>
+      <c r="O22" t="s">
+        <v>26</v>
+      </c>
+      <c r="P22" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" t="s">
         <v>146</v>
       </c>
-      <c r="L22" t="s">
-        <v>45</v>
-      </c>
-      <c r="M22" t="s">
-        <v>15</v>
-      </c>
-      <c r="N22" t="s">
-        <v>39</v>
-      </c>
-      <c r="O22" t="s">
-        <v>40</v>
-      </c>
-      <c r="P22" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>125</v>
-      </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="E23">
         <v>2025</v>
       </c>
       <c r="F23" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G23" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="H23">
         <v>319</v>
       </c>
       <c r="I23" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="L23" t="s">
+        <v>23</v>
+      </c>
+      <c r="M23" t="s">
+        <v>24</v>
+      </c>
+      <c r="N23" t="s">
         <v>152</v>
       </c>
-      <c r="J23" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="L23" t="s">
-        <v>45</v>
-      </c>
-      <c r="M23" t="s">
-        <v>15</v>
-      </c>
-      <c r="N23" t="s">
-        <v>79</v>
-      </c>
       <c r="O23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="E24">
         <v>2023</v>
       </c>
       <c r="F24" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H24">
         <v>975</v>
       </c>
       <c r="I24" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="L24" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="M24" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N24" t="s">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="O24" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="P24" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="2" t="s">
-        <v>85</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="E25">
         <v>2024</v>
       </c>
       <c r="F25" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G25" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H25">
         <v>897</v>
       </c>
       <c r="I25" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="L25" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="M25" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N25" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="O25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="E26">
         <v>2022</v>
       </c>
       <c r="F26" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G26" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H26">
         <v>6309</v>
       </c>
       <c r="I26" t="s">
+        <v>166</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="J26" s="8" t="s">
-        <v>183</v>
-      </c>
       <c r="L26" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>169</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>170</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="E27">
         <v>2024</v>
       </c>
       <c r="F27" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G27" t="s">
-        <v>13</v>
+        <v>172</v>
       </c>
       <c r="H27">
         <v>625</v>
       </c>
       <c r="I27" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="L27" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="M27" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N27" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="O27" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="P27" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" s="2" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="E28">
         <v>2024</v>
       </c>
       <c r="F28" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G28" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H28">
         <v>474</v>
       </c>
       <c r="I28" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="L28" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="M28" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="P28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>180</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>182</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>69</v>
+        <v>183</v>
       </c>
       <c r="E29" s="10">
         <v>2024</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H29" s="10">
         <v>642</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="J29" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="L29" t="s">
+        <v>52</v>
+      </c>
+      <c r="M29" t="s">
+        <v>24</v>
+      </c>
+      <c r="N29" t="s">
+        <v>34</v>
+      </c>
+      <c r="O29" t="s">
+        <v>26</v>
+      </c>
+      <c r="P29" t="s">
         <v>185</v>
-      </c>
-      <c r="L29" t="s">
-        <v>14</v>
-      </c>
-      <c r="M29" t="s">
-        <v>15</v>
-      </c>
-      <c r="N29" t="s">
-        <v>39</v>
-      </c>
-      <c r="O29" t="s">
-        <v>40</v>
-      </c>
-      <c r="P29" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
